--- a/Recommendations.xlsx
+++ b/Recommendations.xlsx
@@ -2722,7 +2722,7 @@
       </c>
       <c r="K80" s="5">
         <f>+K81/K82</f>
-        <v>0.61111111111111116</v>
+        <v>0.59649122807017541</v>
       </c>
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.2">
@@ -2748,8 +2748,8 @@
         <v>86</v>
       </c>
       <c r="K81" s="4">
-        <f>SUM(J3:J72)</f>
-        <v>33</v>
+        <f>SUM(J3:J1000)</f>
+        <v>34</v>
       </c>
       <c r="L81" s="4">
         <f>+K82-K81</f>
@@ -2779,8 +2779,8 @@
         <v>86</v>
       </c>
       <c r="K82" s="4">
-        <f>COUNT(J3:J72)</f>
-        <v>54</v>
+        <f>COUNT(J3:J1000)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.2">
@@ -2856,6 +2856,7 @@
         <v>83</v>
       </c>
       <c r="K85">
+        <f>K81</f>
         <v>34</v>
       </c>
       <c r="L85">
@@ -2886,6 +2887,7 @@
         <v>0</v>
       </c>
       <c r="K86">
+        <f>K82</f>
         <v>57</v>
       </c>
     </row>
